--- a/test/test1.xlsx
+++ b/test/test1.xlsx
@@ -7,7 +7,8 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Scenes" sheetId="1" r:id="rId4"/>
+    <sheet name="Statistics" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,68 +16,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Scene</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Where</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Like, Words, man.</t>
+  </si>
+  <si>
+    <t>Synopsis</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>Making a Scene</t>
+  </si>
+  <si>
+    <t>1st Draft</t>
+  </si>
+  <si>
+    <t>Demonstrate that it’s worth exploring the next scene</t>
+  </si>
+  <si>
+    <t>Another Scene</t>
+  </si>
+  <si>
+    <t>More Scenes</t>
+  </si>
+  <si>
+    <t>An embedded scene</t>
+  </si>
+  <si>
+    <t>Space</t>
+  </si>
+  <si>
+    <t>Jane Cannot Find John</t>
+  </si>
+  <si>
+    <t>We Found John!</t>
+  </si>
+  <si>
+    <t>2nd Draft</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Scene One</t>
+  </si>
+  <si>
+    <t>3rd Draft</t>
+  </si>
+  <si>
+    <t>Scenes</t>
+  </si>
+  <si>
     <t>Words</t>
   </si>
   <si>
-    <t>Point of View</t>
-  </si>
-  <si>
-    <t>Location(s)</t>
-  </si>
-  <si>
-    <t>Focus Character</t>
-  </si>
-  <si>
-    <t>Characters</t>
-  </si>
-  <si>
-    <t>Mentions</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Earth</t>
-  </si>
-  <si>
-    <t>Making a Scene</t>
-  </si>
-  <si>
-    <t>John
-Jane</t>
-  </si>
-  <si>
-    <t>Space</t>
-  </si>
-  <si>
-    <t>Another Scene</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Jane Cannot Find John</t>
-  </si>
-  <si>
-    <t>We Found John!</t>
-  </si>
-  <si>
-    <t>Mars</t>
-  </si>
-  <si>
-    <t>Scene One</t>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0!"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -117,19 +143,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,15 +465,16 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="true" style="0"/>
-    <col min="2" max="2" width="7" customWidth="true" style="0"/>
-    <col min="3" max="3" width="19" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16" customWidth="true" style="0"/>
-    <col min="5" max="5" width="21" customWidth="true" style="0"/>
-    <col min="6" max="6" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="2" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10" customWidth="true" style="0"/>
+    <col min="4" max="4" width="7" customWidth="true" style="0"/>
+    <col min="5" max="5" width="55" customWidth="true" style="0"/>
+    <col min="6" max="6" width="24" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -465,96 +501,295 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4">
+        <v>534</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="4">
+        <v>79</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="4">
+        <v>420</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="4">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="4">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="4">
+        <v>34</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="4">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="F10" s="6">
+        <v>1146</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="12.6" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
-        <v>530</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="6">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1061</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <v>34</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4">
-        <v>108</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="4">
-        <v>55</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
+      <c r="E6" s="6">
+        <v>1146</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1146</v>
       </c>
     </row>
   </sheetData>

--- a/test/test1.xlsx
+++ b/test/test1.xlsx
@@ -16,53 +16,152 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
-  <si>
-    <t>#</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+  <si>
+    <t>Active</t>
   </si>
   <si>
     <t>Scene</t>
   </si>
   <si>
+    <t>Words</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Where</t>
+    <t>Synopsis</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Inciting Incident</t>
   </si>
   <si>
     <t>Goal</t>
   </si>
   <si>
-    <t>Like, Words, man.</t>
-  </si>
-  <si>
-    <t>Synopsis</t>
+    <t>Complication(s)</t>
+  </si>
+  <si>
+    <t>Turning Point</t>
+  </si>
+  <si>
+    <t>Crisis</t>
+  </si>
+  <si>
+    <t>(Non-)Resolution</t>
+  </si>
+  <si>
+    <t>Point of View</t>
+  </si>
+  <si>
+    <t>Period/Time</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Location(s)</t>
+  </si>
+  <si>
+    <t>Focus Character</t>
+  </si>
+  <si>
+    <t>Characters</t>
+  </si>
+  <si>
+    <t>Mentions</t>
+  </si>
+  <si>
+    <t>Pace</t>
+  </si>
+  <si>
+    <t>What does it look like?</t>
+  </si>
+  <si>
+    <t>Quality/cadence in the prose</t>
+  </si>
+  <si>
+    <t>What are the characters feeling emotionally?</t>
+  </si>
+  <si>
+    <t>Jane</t>
   </si>
   <si>
     <t>Earth</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Making a Scene</t>
   </si>
   <si>
     <t>1st Draft</t>
   </si>
   <si>
+    <t>Introduce new users to the basics of novelWriter</t>
+  </si>
+  <si>
+    <t>Someone installed novelWriter and opened the sample project</t>
+  </si>
+  <si>
     <t>Demonstrate that it’s worth exploring the next scene</t>
   </si>
   <si>
+    <t>Has previously used other software and is disoriented by the interface
+A new update allows duplicate tags of the same name</t>
+  </si>
+  <si>
+    <t>Realizes that Markdown syntax is actually very easy to understand and use.</t>
+  </si>
+  <si>
+    <t>Fears the reader needs to learn a completely new language, “Markdown”</t>
+  </si>
+  <si>
+    <t>Axniety about learning a new thing has been addressed.</t>
+  </si>
+  <si>
+    <t>5m</t>
+  </si>
+  <si>
+    <t>John
+Jane</t>
+  </si>
+  <si>
+    <t>Space</t>
+  </si>
+  <si>
+    <t>slow, informative</t>
+  </si>
+  <si>
+    <t>A nominally clean, sparse apartment in a high rise tower.</t>
+  </si>
+  <si>
+    <t>friendly although technical</t>
+  </si>
+  <si>
+    <t>bewilderment, fear.</t>
+  </si>
+  <si>
     <t>Another Scene</t>
   </si>
   <si>
+    <t>This is the first bit
+This is the second bit</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
     <t>More Scenes</t>
   </si>
   <si>
     <t>An embedded scene</t>
   </si>
   <si>
-    <t>Space</t>
-  </si>
-  <si>
     <t>Jane Cannot Find John</t>
   </si>
   <si>
@@ -82,12 +181,6 @@
   </si>
   <si>
     <t>Scenes</t>
-  </si>
-  <si>
-    <t>Words</t>
-  </si>
-  <si>
-    <t>Active</t>
   </si>
   <si>
     <t>Inactive</t>
@@ -100,9 +193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0!"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -149,22 +240,22 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,19 +556,34 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="true" style="0"/>
-    <col min="2" max="2" width="22" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10" customWidth="true" style="0"/>
-    <col min="4" max="4" width="7" customWidth="true" style="0"/>
-    <col min="5" max="5" width="55" customWidth="true" style="0"/>
-    <col min="6" max="6" width="24" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9" customWidth="true" style="0"/>
+    <col min="2" max="2" width="21" customWidth="true" style="0"/>
+    <col min="3" max="3" width="7" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22" customWidth="true" style="0"/>
+    <col min="6" max="6" width="40" customWidth="true" style="0"/>
+    <col min="7" max="7" width="40" customWidth="true" style="0"/>
+    <col min="8" max="8" width="40" customWidth="true" style="0"/>
+    <col min="9" max="9" width="40" customWidth="true" style="0"/>
+    <col min="10" max="10" width="40" customWidth="true" style="0"/>
+    <col min="11" max="11" width="40" customWidth="true" style="0"/>
+    <col min="12" max="12" width="40" customWidth="true" style="0"/>
+    <col min="13" max="13" width="19" customWidth="true" style="0"/>
+    <col min="14" max="14" width="16" customWidth="true" style="0"/>
+    <col min="15" max="15" width="12" customWidth="true" style="0"/>
+    <col min="16" max="16" width="16" customWidth="true" style="0"/>
+    <col min="17" max="17" width="21" customWidth="true" style="0"/>
+    <col min="18" max="18" width="14" customWidth="true" style="0"/>
+    <col min="19" max="19" width="12" customWidth="true" style="0"/>
+    <col min="20" max="20" width="17" customWidth="true" style="0"/>
+    <col min="21" max="21" width="40" customWidth="true" style="0"/>
+    <col min="22" max="22" width="40" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,155 +605,265 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="4">
+        <v>534</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4">
+        <v>79</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4">
+        <v>420</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4">
-        <v>534</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="4">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="4">
-        <v>420</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="4">
-        <v>7</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4">
+        <v>27</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="4">
         <v>21</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="4">
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4">
+        <v>49</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="F10" s="6">
+      <c r="C9" s="4">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="C10" s="4">
         <v>1146</v>
       </c>
     </row>
@@ -671,52 +887,52 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="4">
         <v>5</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>0</v>
       </c>
       <c r="D3" s="7">
         <v>5</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>1061</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="7">
@@ -724,22 +940,22 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>34</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="7">
@@ -747,22 +963,22 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>51</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="7">
@@ -770,22 +986,22 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="7">
         <v>7</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>1146</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="7">

--- a/test/test1.xlsx
+++ b/test/test1.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Scenes" sheetId="1" r:id="rId4"/>
     <sheet name="Statistics" sheetId="2" r:id="rId5"/>
+    <sheet name="Characters" sheetId="3" r:id="rId6"/>
+    <sheet name="Locations" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -16,12 +18,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="97">
+  <si>
+    <t>Novel</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>Scene</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Words</t>
@@ -33,6 +41,12 @@
     <t>Synopsis</t>
   </si>
   <si>
+    <t>Value Shift</t>
+  </si>
+  <si>
+    <t>Polarity Shift</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -51,40 +65,91 @@
     <t>Crisis</t>
   </si>
   <si>
+    <t>Climax</t>
+  </si>
+  <si>
     <t>(Non-)Resolution</t>
   </si>
   <si>
+    <t>This Scene is About</t>
+  </si>
+  <si>
+    <t>Impact of the scene</t>
+  </si>
+  <si>
     <t>Point of View</t>
   </si>
   <si>
+    <t>Plot</t>
+  </si>
+  <si>
     <t>Period/Time</t>
   </si>
   <si>
+    <t>Time of Day</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
     <t>Location(s)</t>
   </si>
   <si>
+    <t>Timelines</t>
+  </si>
+  <si>
     <t>Focus Character</t>
   </si>
   <si>
     <t>Characters</t>
   </si>
   <si>
+    <t>Off-stage Characters</t>
+  </si>
+  <si>
+    <t>Entities</t>
+  </si>
+  <si>
+    <t>Objects</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
     <t>Mentions</t>
   </si>
   <si>
+    <t>References</t>
+  </si>
+  <si>
     <t>Pace</t>
   </si>
   <si>
-    <t>What does it look like?</t>
-  </si>
-  <si>
-    <t>Quality/cadence in the prose</t>
-  </si>
-  <si>
-    <t>What are the characters feeling emotionally?</t>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Appearance</t>
+  </si>
+  <si>
+    <t>Tactile</t>
+  </si>
+  <si>
+    <t>Environmental Sounds</t>
+  </si>
+  <si>
+    <t>Environmental Smells</t>
+  </si>
+  <si>
+    <t>Clothing</t>
+  </si>
+  <si>
+    <t>Prose Quality/Cadence</t>
+  </si>
+  <si>
+    <t>Emotions</t>
+  </si>
+  <si>
+    <t>Additional Notes</t>
   </si>
   <si>
     <t>Jane</t>
@@ -174,6 +239,9 @@
     <t>Mars</t>
   </si>
   <si>
+    <t>Sequel</t>
+  </si>
+  <si>
     <t>Scene One</t>
   </si>
   <si>
@@ -187,6 +255,63 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>Folder</t>
+  </si>
+  <si>
+    <t>Given</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>Pronouns</t>
+  </si>
+  <si>
+    <t>Fate</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>John | John Smith</t>
+  </si>
+  <si>
+    <t>Main Characters</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>he/him</t>
+  </si>
+  <si>
+    <t>Happy farmer</t>
+  </si>
+  <si>
+    <t>The sidekick</t>
+  </si>
+  <si>
+    <t>Jane Smith</t>
+  </si>
+  <si>
+    <t>Jane | Jane Smith</t>
+  </si>
+  <si>
+    <t>she/her</t>
+  </si>
+  <si>
+    <t>Finds John</t>
+  </si>
+  <si>
+    <t>The heroine</t>
+  </si>
+  <si>
+    <t>FreemanHome</t>
   </si>
 </sst>
 </file>
@@ -234,13 +359,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
@@ -248,11 +370,20 @@
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
@@ -556,34 +687,56 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="21" customWidth="true" style="0"/>
-    <col min="3" max="3" width="7" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22" customWidth="true" style="0"/>
-    <col min="6" max="6" width="40" customWidth="true" style="0"/>
-    <col min="7" max="7" width="40" customWidth="true" style="0"/>
-    <col min="8" max="8" width="40" customWidth="true" style="0"/>
-    <col min="9" max="9" width="40" customWidth="true" style="0"/>
+    <col min="1" max="1" width="7.3" customWidth="true" style="0"/>
+    <col min="2" max="2" width="2.65" customWidth="true" style="0"/>
+    <col min="3" max="3" width="9" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.05" customWidth="true" style="0"/>
+    <col min="5" max="5" width="7" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.05" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20.5" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16" customWidth="true" style="0"/>
+    <col min="9" max="9" width="20" customWidth="true" style="0"/>
     <col min="10" max="10" width="40" customWidth="true" style="0"/>
     <col min="11" max="11" width="40" customWidth="true" style="0"/>
     <col min="12" max="12" width="40" customWidth="true" style="0"/>
-    <col min="13" max="13" width="19" customWidth="true" style="0"/>
-    <col min="14" max="14" width="16" customWidth="true" style="0"/>
-    <col min="15" max="15" width="12" customWidth="true" style="0"/>
-    <col min="16" max="16" width="16" customWidth="true" style="0"/>
-    <col min="17" max="17" width="21" customWidth="true" style="0"/>
-    <col min="18" max="18" width="14" customWidth="true" style="0"/>
-    <col min="19" max="19" width="12" customWidth="true" style="0"/>
-    <col min="20" max="20" width="17" customWidth="true" style="0"/>
-    <col min="21" max="21" width="40" customWidth="true" style="0"/>
-    <col min="22" max="22" width="40" customWidth="true" style="0"/>
+    <col min="13" max="13" width="40" customWidth="true" style="0"/>
+    <col min="14" max="14" width="40" customWidth="true" style="0"/>
+    <col min="15" max="15" width="40" customWidth="true" style="0"/>
+    <col min="16" max="16" width="9" customWidth="true" style="0"/>
+    <col min="17" max="17" width="40" customWidth="true" style="0"/>
+    <col min="18" max="18" width="27" customWidth="true" style="0"/>
+    <col min="19" max="19" width="27" customWidth="true" style="0"/>
+    <col min="20" max="20" width="19" customWidth="true" style="0"/>
+    <col min="21" max="21" width="6" customWidth="true" style="0"/>
+    <col min="22" max="22" width="16" customWidth="true" style="0"/>
+    <col min="23" max="23" width="16" customWidth="true" style="0"/>
+    <col min="24" max="24" width="12" customWidth="true" style="0"/>
+    <col min="25" max="25" width="16" customWidth="true" style="0"/>
+    <col min="26" max="26" width="13" customWidth="true" style="0"/>
+    <col min="27" max="27" width="21" customWidth="true" style="0"/>
+    <col min="28" max="28" width="14" customWidth="true" style="0"/>
+    <col min="29" max="29" width="28" customWidth="true" style="0"/>
+    <col min="30" max="30" width="12" customWidth="true" style="0"/>
+    <col min="31" max="31" width="10" customWidth="true" style="0"/>
+    <col min="32" max="32" width="9" customWidth="true" style="0"/>
+    <col min="33" max="33" width="12" customWidth="true" style="0"/>
+    <col min="34" max="34" width="14" customWidth="true" style="0"/>
+    <col min="35" max="35" width="17.65" customWidth="true" style="0"/>
+    <col min="36" max="36" width="10" customWidth="true" style="0"/>
+    <col min="37" max="37" width="40" customWidth="true" style="0"/>
+    <col min="38" max="38" width="10" customWidth="true" style="0"/>
+    <col min="39" max="39" width="28" customWidth="true" style="0"/>
+    <col min="40" max="40" width="28" customWidth="true" style="0"/>
+    <col min="41" max="41" width="12" customWidth="true" style="0"/>
+    <col min="42" max="42" width="30" customWidth="true" style="0"/>
+    <col min="43" max="43" width="20.35" customWidth="true" style="0"/>
+    <col min="44" max="44" width="23" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,217 +806,598 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
-      <c r="M2" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:23">
-      <c r="A3" s="3" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="4">
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="5"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="8"/>
+    </row>
+    <row r="3" spans="1:44">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3">
         <v>534</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="5"/>
+      <c r="V3" s="6">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR3" s="8"/>
+    </row>
+    <row r="4" spans="1:44">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3">
+        <v>79</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="5"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="8"/>
+    </row>
+    <row r="5" spans="1:44">
+      <c r="A5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="3">
+        <v>420</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U5" s="5"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="8"/>
+    </row>
+    <row r="6" spans="1:44">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U6" s="5"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+      <c r="AR6" s="8"/>
+    </row>
+    <row r="7" spans="1:44">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" s="5"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="2"/>
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
+      <c r="AR7" s="8"/>
+    </row>
+    <row r="8" spans="1:44">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="3">
         <v>34</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="4">
-        <v>79</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="4">
-        <v>420</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="U8" s="5"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="2"/>
+      <c r="AM8" s="2"/>
+      <c r="AN8" s="2"/>
+      <c r="AO8" s="2"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+      <c r="AR8" s="8"/>
+    </row>
+    <row r="9" spans="1:44">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="4">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="4">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="4">
-        <v>51</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="C10" s="4">
+      <c r="U9" s="5"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="8"/>
+    </row>
+    <row r="10" spans="1:44">
+      <c r="E10" s="3">
         <v>1146</v>
       </c>
     </row>
@@ -887,126 +1421,317 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1061</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="3">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1146</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1146</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.1" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.25" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.95" customWidth="true" style="0"/>
+    <col min="5" max="5" width="7" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12" customWidth="true" style="0"/>
+    <col min="8" max="8" width="14.2" customWidth="true" style="0"/>
+    <col min="9" max="9" width="12.4" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="4">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1061</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
+    <col min="2" max="2" width="6.85" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14.95" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>51</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="4">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1146</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1146</v>
-      </c>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/test/test1.xlsx
+++ b/test/test1.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Statistics" sheetId="2" r:id="rId5"/>
     <sheet name="Characters" sheetId="3" r:id="rId6"/>
     <sheet name="Locations" sheetId="4" r:id="rId7"/>
+    <sheet name="Analysis" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -18,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="97">
-  <si>
-    <t>Novel</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>Active</t>
   </si>
@@ -41,12 +36,6 @@
     <t>Synopsis</t>
   </si>
   <si>
-    <t>Value Shift</t>
-  </si>
-  <si>
-    <t>Polarity Shift</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -65,84 +54,36 @@
     <t>Crisis</t>
   </si>
   <si>
-    <t>Climax</t>
-  </si>
-  <si>
     <t>(Non-)Resolution</t>
   </si>
   <si>
-    <t>This Scene is About</t>
-  </si>
-  <si>
-    <t>Impact of the scene</t>
-  </si>
-  <si>
     <t>Point of View</t>
   </si>
   <si>
-    <t>Plot</t>
-  </si>
-  <si>
     <t>Period/Time</t>
   </si>
   <si>
-    <t>Time of Day</t>
-  </si>
-  <si>
     <t>Duration</t>
   </si>
   <si>
     <t>Location(s)</t>
   </si>
   <si>
-    <t>Timelines</t>
-  </si>
-  <si>
     <t>Focus Character</t>
   </si>
   <si>
     <t>Characters</t>
   </si>
   <si>
-    <t>Off-stage Characters</t>
-  </si>
-  <si>
-    <t>Entities</t>
-  </si>
-  <si>
-    <t>Objects</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
     <t>Mentions</t>
   </si>
   <si>
-    <t>References</t>
-  </si>
-  <si>
     <t>Pace</t>
   </si>
   <si>
-    <t>Weather</t>
-  </si>
-  <si>
     <t>Appearance</t>
   </si>
   <si>
-    <t>Tactile</t>
-  </si>
-  <si>
-    <t>Environmental Sounds</t>
-  </si>
-  <si>
-    <t>Environmental Smells</t>
-  </si>
-  <si>
-    <t>Clothing</t>
-  </si>
-  <si>
     <t>Prose Quality/Cadence</t>
   </si>
   <si>
@@ -152,10 +93,10 @@
     <t>Additional Notes</t>
   </si>
   <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Earth</t>
+    <t xml:space="preserve"> Sl</t>
+  </si>
+  <si>
+    <t>User Defined</t>
   </si>
   <si>
     <t>yes</t>
@@ -189,7 +130,13 @@
     <t>Axniety about learning a new thing has been addressed.</t>
   </si>
   <si>
+    <t>Jane</t>
+  </si>
+  <si>
     <t>5m</t>
+  </si>
+  <si>
+    <t>Earth</t>
   </si>
   <si>
     <t>John
@@ -211,6 +158,12 @@
     <t>bewilderment, fear.</t>
   </si>
   <si>
+    <t>Footnote.f4xr5: Using a non-breaking space is the correct way to separate a number from its unit. This ensures that line wrapping does not split the two.</t>
+  </si>
+  <si>
+    <t>something.</t>
+  </si>
+  <si>
     <t>Another Scene</t>
   </si>
   <si>
@@ -239,9 +192,6 @@
     <t>Mars</t>
   </si>
   <si>
-    <t>Sequel</t>
-  </si>
-  <si>
     <t>Scene One</t>
   </si>
   <si>
@@ -272,6 +222,9 @@
     <t>Pronouns</t>
   </si>
   <si>
+    <t>Age</t>
+  </si>
+  <si>
     <t>Fate</t>
   </si>
   <si>
@@ -312,6 +265,120 @@
   </si>
   <si>
     <t>FreemanHome</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Phrase</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>you</t>
+  </si>
+  <si>
+    <t>can</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>this</t>
+  </si>
+  <si>
+    <t>as</t>
+  </si>
+  <si>
+    <t>scene</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>chapter</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
+    <t>heading</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>files</t>
+  </si>
+  <si>
+    <t>three</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>adding</t>
+  </si>
+  <si>
+    <t>more</t>
+  </si>
+  <si>
+    <t>scenes</t>
+  </si>
+  <si>
+    <t>be</t>
+  </si>
+  <si>
+    <t>you can</t>
+  </si>
+  <si>
+    <t>in the</t>
+  </si>
+  <si>
+    <t>level three</t>
+  </si>
+  <si>
+    <t>three heading</t>
+  </si>
+  <si>
+    <t>level three heading</t>
+  </si>
+  <si>
+    <t>adding more</t>
   </si>
 </sst>
 </file>
@@ -359,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -374,19 +441,16 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,56 +751,38 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="7.3" customWidth="true" style="0"/>
-    <col min="2" max="2" width="2.65" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9" customWidth="true" style="0"/>
-    <col min="4" max="4" width="23.05" customWidth="true" style="0"/>
-    <col min="5" max="5" width="7" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.05" customWidth="true" style="0"/>
-    <col min="7" max="7" width="20.5" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16" customWidth="true" style="0"/>
-    <col min="9" max="9" width="20" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.84" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22.45" customWidth="true" style="0"/>
+    <col min="3" max="3" width="7.26" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.45" customWidth="true" style="0"/>
+    <col min="5" max="5" width="19.3" customWidth="true" style="0"/>
+    <col min="6" max="6" width="40" customWidth="true" style="0"/>
+    <col min="7" max="7" width="40" customWidth="true" style="0"/>
+    <col min="8" max="8" width="40" customWidth="true" style="0"/>
+    <col min="9" max="9" width="40" customWidth="true" style="0"/>
     <col min="10" max="10" width="40" customWidth="true" style="0"/>
     <col min="11" max="11" width="40" customWidth="true" style="0"/>
     <col min="12" max="12" width="40" customWidth="true" style="0"/>
-    <col min="13" max="13" width="40" customWidth="true" style="0"/>
-    <col min="14" max="14" width="40" customWidth="true" style="0"/>
-    <col min="15" max="15" width="40" customWidth="true" style="0"/>
-    <col min="16" max="16" width="9" customWidth="true" style="0"/>
-    <col min="17" max="17" width="40" customWidth="true" style="0"/>
-    <col min="18" max="18" width="27" customWidth="true" style="0"/>
-    <col min="19" max="19" width="27" customWidth="true" style="0"/>
-    <col min="20" max="20" width="19" customWidth="true" style="0"/>
-    <col min="21" max="21" width="6" customWidth="true" style="0"/>
-    <col min="22" max="22" width="16" customWidth="true" style="0"/>
-    <col min="23" max="23" width="16" customWidth="true" style="0"/>
-    <col min="24" max="24" width="12" customWidth="true" style="0"/>
-    <col min="25" max="25" width="16" customWidth="true" style="0"/>
-    <col min="26" max="26" width="13" customWidth="true" style="0"/>
-    <col min="27" max="27" width="21" customWidth="true" style="0"/>
-    <col min="28" max="28" width="14" customWidth="true" style="0"/>
-    <col min="29" max="29" width="28" customWidth="true" style="0"/>
-    <col min="30" max="30" width="12" customWidth="true" style="0"/>
-    <col min="31" max="31" width="10" customWidth="true" style="0"/>
-    <col min="32" max="32" width="9" customWidth="true" style="0"/>
-    <col min="33" max="33" width="12" customWidth="true" style="0"/>
-    <col min="34" max="34" width="14" customWidth="true" style="0"/>
-    <col min="35" max="35" width="17.65" customWidth="true" style="0"/>
-    <col min="36" max="36" width="10" customWidth="true" style="0"/>
-    <col min="37" max="37" width="40" customWidth="true" style="0"/>
-    <col min="38" max="38" width="10" customWidth="true" style="0"/>
-    <col min="39" max="39" width="28" customWidth="true" style="0"/>
-    <col min="40" max="40" width="28" customWidth="true" style="0"/>
-    <col min="41" max="41" width="12" customWidth="true" style="0"/>
-    <col min="42" max="42" width="30" customWidth="true" style="0"/>
-    <col min="43" max="43" width="20.35" customWidth="true" style="0"/>
-    <col min="44" max="44" width="23" customWidth="true" style="0"/>
+    <col min="13" max="13" width="14.94" customWidth="true" style="0"/>
+    <col min="14" max="14" width="14.58" customWidth="true" style="0"/>
+    <col min="15" max="15" width="9.36" customWidth="true" style="0"/>
+    <col min="16" max="16" width="11.7" customWidth="true" style="0"/>
+    <col min="17" max="17" width="18.9" customWidth="true" style="0"/>
+    <col min="18" max="18" width="12.6" customWidth="true" style="0"/>
+    <col min="19" max="19" width="9.6" customWidth="true" style="0"/>
+    <col min="20" max="20" width="17.05" customWidth="true" style="0"/>
+    <col min="21" max="21" width="40" customWidth="true" style="0"/>
+    <col min="22" max="22" width="26.7" customWidth="true" style="0"/>
+    <col min="23" max="23" width="19.15" customWidth="true" style="0"/>
+    <col min="24" max="24" width="40" customWidth="true" style="0"/>
+    <col min="25" max="25" width="3.06" customWidth="true" style="0"/>
+    <col min="26" max="26" width="15.12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,590 +861,330 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="C2" s="3">
+        <v>532</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="P2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="Q2" s="7"/>
+      <c r="R2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:44">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="4" t="s">
+      <c r="W2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="5"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="4" t="s">
+      <c r="X2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="8"/>
-    </row>
-    <row r="3" spans="1:44">
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3">
+        <v>79</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3">
-        <v>534</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="N3" s="5"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U3" s="5"/>
-      <c r="V3" s="6">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2"/>
-      <c r="X3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AR3" s="8"/>
-    </row>
-    <row r="4" spans="1:44">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>46</v>
+      <c r="C4" s="3">
+        <v>420</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3">
-        <v>79</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="5"/>
-      <c r="V4" s="6"/>
+      <c r="M4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="8"/>
-    </row>
-    <row r="5" spans="1:44">
+      <c r="X4" s="8"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="3">
-        <v>420</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U5" s="5"/>
-      <c r="V5" s="6"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
-      <c r="AR5" s="8"/>
-    </row>
-    <row r="6" spans="1:44">
+      <c r="X5" s="8"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3">
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="3">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U6" s="5"/>
-      <c r="V6" s="6"/>
+      <c r="M6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="8"/>
-    </row>
-    <row r="7" spans="1:44">
+      <c r="X6" s="8"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="3">
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3">
-        <v>21</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U7" s="5"/>
-      <c r="V7" s="6"/>
+      <c r="M7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
-      <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-      <c r="AR7" s="8"/>
-    </row>
-    <row r="8" spans="1:44">
+      <c r="X7" s="8"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3">
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U8" s="5"/>
-      <c r="V8" s="6"/>
+      <c r="M8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-      <c r="AR8" s="8"/>
-    </row>
-    <row r="9" spans="1:44">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="3">
-        <v>51</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" s="5"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="8"/>
-    </row>
-    <row r="10" spans="1:44">
-      <c r="E10" s="3">
-        <v>1146</v>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="C9" s="3">
+        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -1416,43 +1202,43 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.6" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.45" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -1460,22 +1246,22 @@
       <c r="C3" s="3">
         <v>0</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="3">
         <v>5</v>
       </c>
       <c r="E3" s="3">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="9">
-        <v>1061</v>
+      <c r="G3" s="3">
+        <v>1058</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1483,7 +1269,7 @@
       <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="3">
@@ -1492,13 +1278,13 @@
       <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="3">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1506,7 +1292,7 @@
       <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
       <c r="E5" s="3">
@@ -1515,13 +1301,13 @@
       <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="3">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3">
         <v>7</v>
@@ -1529,17 +1315,17 @@
       <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="3">
         <v>7</v>
       </c>
       <c r="E6" s="3">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
-        <v>1146</v>
+      <c r="G6" s="3">
+        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -1557,13 +1343,13 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.1" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.25" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.95" customWidth="true" style="0"/>
-    <col min="5" max="5" width="7" customWidth="true" style="0"/>
-    <col min="6" max="6" width="10" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12" customWidth="true" style="0"/>
+    <col min="1" max="1" width="11.5" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.65" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.35" customWidth="true" style="0"/>
+    <col min="4" max="4" width="6.3" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.26" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.8" customWidth="true" style="0"/>
+    <col min="7" max="7" width="4.5" customWidth="true" style="0"/>
     <col min="8" max="8" width="14.2" customWidth="true" style="0"/>
     <col min="9" max="9" width="12.4" customWidth="true" style="0"/>
   </cols>
@@ -1573,86 +1359,84 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1667,71 +1451,358 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.85" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14.95" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.85" customWidth="true" style="0"/>
+    <col min="2" max="2" width="14.95" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.7" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="6.75" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.06" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.35" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.06" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="3">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="3">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="3">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="3">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="B14" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="3">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/test/test1.xlsx
+++ b/test/test1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="399">
   <si>
     <t>Active</t>
   </si>
@@ -117,8 +117,8 @@
     <t>Demonstrate that it’s worth exploring the next scene</t>
   </si>
   <si>
-    <t>Has previously used other software and is disoriented by the interface
-A new update allows duplicate tags of the same name</t>
+    <t>A new update allows duplicate tags of the same name
+Has previously used other software and is disoriented by the interface</t>
   </si>
   <si>
     <t>Realizes that Markdown syntax is actually very easy to understand and use.</t>
@@ -139,8 +139,8 @@
     <t>Earth</t>
   </si>
   <si>
-    <t>John
-Jane</t>
+    <t>Jane
+John</t>
   </si>
   <si>
     <t>Space</t>
@@ -273,6 +273,12 @@
     <t>Frequency</t>
   </si>
   <si>
+    <t>Clumpiness</t>
+  </si>
+  <si>
+    <t>Avg. Clump</t>
+  </si>
+  <si>
     <t>Phrase</t>
   </si>
   <si>
@@ -306,10 +312,13 @@
     <t>level</t>
   </si>
   <si>
+    <t>as</t>
+  </si>
+  <si>
     <t>this</t>
   </si>
   <si>
-    <t>as</t>
+    <t>if</t>
   </si>
   <si>
     <t>scene</t>
@@ -318,51 +327,273 @@
     <t>for</t>
   </si>
   <si>
-    <t>if</t>
-  </si>
-  <si>
     <t>chapter</t>
   </si>
   <si>
     <t>also</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>heading</t>
   </si>
   <si>
-    <t>text</t>
+    <t>files</t>
+  </si>
+  <si>
+    <t>file</t>
   </si>
   <si>
     <t>add</t>
   </si>
   <si>
-    <t>file</t>
-  </si>
-  <si>
-    <t>files</t>
+    <t>all</t>
   </si>
   <si>
     <t>three</t>
   </si>
   <si>
-    <t>all</t>
+    <t>adding</t>
+  </si>
+  <si>
+    <t>more</t>
+  </si>
+  <si>
+    <t>scenes</t>
   </si>
   <si>
     <t>with</t>
   </si>
   <si>
-    <t>adding</t>
-  </si>
-  <si>
-    <t>more</t>
-  </si>
-  <si>
-    <t>scenes</t>
-  </si>
-  <si>
     <t>be</t>
   </si>
   <si>
+    <t>like</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>too</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>which</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>that</t>
+  </si>
+  <si>
+    <t>just</t>
+  </si>
+  <si>
+    <t>your</t>
+  </si>
+  <si>
+    <t>want</t>
+  </si>
+  <si>
+    <t>way</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>another</t>
+  </si>
+  <si>
+    <t>works</t>
+  </si>
+  <si>
+    <t>structure</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>wish</t>
+  </si>
+  <si>
+    <t>novelwriter</t>
+  </si>
+  <si>
+    <t>cares</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>headings</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>they</t>
+  </si>
+  <si>
+    <t>appear</t>
+  </si>
+  <si>
+    <t>paragraph</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>have</t>
+  </si>
+  <si>
+    <t>bold</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>formatting</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>margin</t>
+  </si>
+  <si>
+    <t>was</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>italic</t>
+  </si>
+  <si>
+    <t>spaces</t>
+  </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>document</t>
+  </si>
+  <si>
+    <t>are</t>
+  </si>
+  <si>
+    <t>supports</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>will</t>
+  </si>
+  <si>
+    <t>jane</t>
+  </si>
+  <si>
+    <t>novel</t>
+  </si>
+  <si>
+    <t>sup</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>thin</t>
+  </si>
+  <si>
+    <t>script</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>there</t>
+  </si>
+  <si>
+    <t>some</t>
+  </si>
+  <si>
+    <t>dashes</t>
+  </si>
+  <si>
+    <t>mars</t>
+  </si>
+  <si>
+    <t>titles</t>
+  </si>
+  <si>
+    <t>alignment</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>writer</t>
+  </si>
+  <si>
+    <t>supported</t>
+  </si>
+  <si>
+    <t>novels</t>
+  </si>
+  <si>
+    <t>emphasis</t>
+  </si>
+  <si>
+    <t>shortcodes</t>
+  </si>
+  <si>
+    <t>symbols</t>
+  </si>
+  <si>
+    <t>quotes</t>
+  </si>
+  <si>
     <t>you can</t>
   </si>
   <si>
@@ -379,6 +610,615 @@
   </si>
   <si>
     <t>adding more</t>
+  </si>
+  <si>
+    <t>the same</t>
+  </si>
+  <si>
+    <t>the chapter</t>
+  </si>
+  <si>
+    <t>can be</t>
+  </si>
+  <si>
+    <t>in the same</t>
+  </si>
+  <si>
+    <t>of the</t>
+  </si>
+  <si>
+    <t>if you</t>
+  </si>
+  <si>
+    <t>with a</t>
+  </si>
+  <si>
+    <t>and the</t>
+  </si>
+  <si>
+    <t>same file</t>
+  </si>
+  <si>
+    <t>the same file</t>
+  </si>
+  <si>
+    <t>a level</t>
+  </si>
+  <si>
+    <t>a level three</t>
+  </si>
+  <si>
+    <t>can of</t>
+  </si>
+  <si>
+    <t>you can of</t>
+  </si>
+  <si>
+    <t>of course</t>
+  </si>
+  <si>
+    <t>can of course</t>
+  </si>
+  <si>
+    <t>the level</t>
+  </si>
+  <si>
+    <t>files in</t>
+  </si>
+  <si>
+    <t>you want</t>
+  </si>
+  <si>
+    <t>want to</t>
+  </si>
+  <si>
+    <t>you want to</t>
+  </si>
+  <si>
+    <t>is the</t>
+  </si>
+  <si>
+    <t>more scenes</t>
+  </si>
+  <si>
+    <t>scenes to</t>
+  </si>
+  <si>
+    <t>more scenes to</t>
+  </si>
+  <si>
+    <t>to a</t>
+  </si>
+  <si>
+    <t>scenes to a</t>
+  </si>
+  <si>
+    <t>a chapter</t>
+  </si>
+  <si>
+    <t>to a chapter</t>
+  </si>
+  <si>
+    <t>chapter is</t>
+  </si>
+  <si>
+    <t>a chapter is</t>
+  </si>
+  <si>
+    <t>is as</t>
+  </si>
+  <si>
+    <t>chapter is as</t>
+  </si>
+  <si>
+    <t>as easy</t>
+  </si>
+  <si>
+    <t>is as easy</t>
+  </si>
+  <si>
+    <t>easy as</t>
+  </si>
+  <si>
+    <t>as easy as</t>
+  </si>
+  <si>
+    <t>as adding</t>
+  </si>
+  <si>
+    <t>easy as adding</t>
+  </si>
+  <si>
+    <t>as adding more</t>
+  </si>
+  <si>
+    <t>more scene</t>
+  </si>
+  <si>
+    <t>adding more scene</t>
+  </si>
+  <si>
+    <t>scene files</t>
+  </si>
+  <si>
+    <t>more scene files</t>
+  </si>
+  <si>
+    <t>files with</t>
+  </si>
+  <si>
+    <t>scene files with</t>
+  </si>
+  <si>
+    <t>files with a</t>
+  </si>
+  <si>
+    <t>with a level</t>
+  </si>
+  <si>
+    <t>heading you</t>
+  </si>
+  <si>
+    <t>three heading you</t>
+  </si>
+  <si>
+    <t>heading you can</t>
+  </si>
+  <si>
+    <t>course also</t>
+  </si>
+  <si>
+    <t>of course also</t>
+  </si>
+  <si>
+    <t>also just</t>
+  </si>
+  <si>
+    <t>course also just</t>
+  </si>
+  <si>
+    <t>just add</t>
+  </si>
+  <si>
+    <t>also just add</t>
+  </si>
+  <si>
+    <t>add another</t>
+  </si>
+  <si>
+    <t>just add another</t>
+  </si>
+  <si>
+    <t>another level</t>
+  </si>
+  <si>
+    <t>add another level</t>
+  </si>
+  <si>
+    <t>another level three</t>
+  </si>
+  <si>
+    <t>heading in</t>
+  </si>
+  <si>
+    <t>three heading in</t>
+  </si>
+  <si>
+    <t>heading in the</t>
+  </si>
+  <si>
+    <t>file if</t>
+  </si>
+  <si>
+    <t>same file if</t>
+  </si>
+  <si>
+    <t>if that</t>
+  </si>
+  <si>
+    <t>file if that</t>
+  </si>
+  <si>
+    <t>that works</t>
+  </si>
+  <si>
+    <t>if that works</t>
+  </si>
+  <si>
+    <t>works for</t>
+  </si>
+  <si>
+    <t>that works for</t>
+  </si>
+  <si>
+    <t>for the</t>
+  </si>
+  <si>
+    <t>works for the</t>
+  </si>
+  <si>
+    <t>the way</t>
+  </si>
+  <si>
+    <t>for the way</t>
+  </si>
+  <si>
+    <t>way you</t>
+  </si>
+  <si>
+    <t>the way you</t>
+  </si>
+  <si>
+    <t>way you want</t>
+  </si>
+  <si>
+    <t>to structure</t>
+  </si>
+  <si>
+    <t>want to structure</t>
+  </si>
+  <si>
+    <t>structure your</t>
+  </si>
+  <si>
+    <t>to structure your</t>
+  </si>
+  <si>
+    <t>your files</t>
+  </si>
+  <si>
+    <t>structure your files</t>
+  </si>
+  <si>
+    <t>your files in</t>
+  </si>
+  <si>
+    <t>in fact</t>
+  </si>
+  <si>
+    <t>files in fact</t>
+  </si>
+  <si>
+    <t>fact if</t>
+  </si>
+  <si>
+    <t>in fact if</t>
+  </si>
+  <si>
+    <t>fact if you</t>
+  </si>
+  <si>
+    <t>you wish</t>
+  </si>
+  <si>
+    <t>if you wish</t>
+  </si>
+  <si>
+    <t>wish you</t>
+  </si>
+  <si>
+    <t>you wish you</t>
+  </si>
+  <si>
+    <t>wish you can</t>
+  </si>
+  <si>
+    <t>can add</t>
+  </si>
+  <si>
+    <t>you can add</t>
+  </si>
+  <si>
+    <t>add all</t>
+  </si>
+  <si>
+    <t>can add all</t>
+  </si>
+  <si>
+    <t>all the</t>
+  </si>
+  <si>
+    <t>add all the</t>
+  </si>
+  <si>
+    <t>the scenes</t>
+  </si>
+  <si>
+    <t>all the scenes</t>
+  </si>
+  <si>
+    <t>scenes in</t>
+  </si>
+  <si>
+    <t>the scenes in</t>
+  </si>
+  <si>
+    <t>scenes in the</t>
+  </si>
+  <si>
+    <t>in the chapter</t>
+  </si>
+  <si>
+    <t>chapter file</t>
+  </si>
+  <si>
+    <t>the chapter file</t>
+  </si>
+  <si>
+    <t>file too</t>
+  </si>
+  <si>
+    <t>chapter file too</t>
+  </si>
+  <si>
+    <t>too all</t>
+  </si>
+  <si>
+    <t>file too all</t>
+  </si>
+  <si>
+    <t>all novelwriter</t>
+  </si>
+  <si>
+    <t>too all novelwriter</t>
+  </si>
+  <si>
+    <t>novelwriter cares</t>
+  </si>
+  <si>
+    <t>all novelwriter cares</t>
+  </si>
+  <si>
+    <t>cares about</t>
+  </si>
+  <si>
+    <t>novelwriter cares about</t>
+  </si>
+  <si>
+    <t>about is</t>
+  </si>
+  <si>
+    <t>cares about is</t>
+  </si>
+  <si>
+    <t>about is the</t>
+  </si>
+  <si>
+    <t>is the level</t>
+  </si>
+  <si>
+    <t>level of</t>
+  </si>
+  <si>
+    <t>the level of</t>
+  </si>
+  <si>
+    <t>level of the</t>
+  </si>
+  <si>
+    <t>the headings</t>
+  </si>
+  <si>
+    <t>of the headings</t>
+  </si>
+  <si>
+    <t>headings and</t>
+  </si>
+  <si>
+    <t>the headings and</t>
+  </si>
+  <si>
+    <t>headings and the</t>
+  </si>
+  <si>
+    <t>the order</t>
+  </si>
+  <si>
+    <t>and the order</t>
+  </si>
+  <si>
+    <t>order in</t>
+  </si>
+  <si>
+    <t>the order in</t>
+  </si>
+  <si>
+    <t>in which</t>
+  </si>
+  <si>
+    <t>order in which</t>
+  </si>
+  <si>
+    <t>which they</t>
+  </si>
+  <si>
+    <t>in which they</t>
+  </si>
+  <si>
+    <t>they appear</t>
+  </si>
+  <si>
+    <t>which they appear</t>
+  </si>
+  <si>
+    <t>can also</t>
+  </si>
+  <si>
+    <t>you can also</t>
+  </si>
+  <si>
+    <t>adding more scenes</t>
+  </si>
+  <si>
+    <t>text is</t>
+  </si>
+  <si>
+    <t>appear adding</t>
+  </si>
+  <si>
+    <t>they appear adding</t>
+  </si>
+  <si>
+    <t>appear adding more</t>
+  </si>
+  <si>
+    <t>this text</t>
+  </si>
+  <si>
+    <t>this text is</t>
+  </si>
+  <si>
+    <t>the scene</t>
+  </si>
+  <si>
+    <t>the left</t>
+  </si>
+  <si>
+    <t>like the</t>
+  </si>
+  <si>
+    <t>the text</t>
+  </si>
+  <si>
+    <t>this is</t>
+  </si>
+  <si>
+    <t>to the</t>
+  </si>
+  <si>
+    <t>bold italic</t>
+  </si>
+  <si>
+    <t>the first</t>
+  </si>
+  <si>
+    <t>on mars</t>
+  </si>
+  <si>
+    <t>titles can</t>
+  </si>
+  <si>
+    <t>titles can be</t>
+  </si>
+  <si>
+    <t>from both</t>
+  </si>
+  <si>
+    <t>both the</t>
+  </si>
+  <si>
+    <t>from both the</t>
+  </si>
+  <si>
+    <t>both the left</t>
+  </si>
+  <si>
+    <t>right margin</t>
+  </si>
+  <si>
+    <t>he was</t>
+  </si>
+  <si>
+    <t>the writer</t>
+  </si>
+  <si>
+    <t>are also</t>
+  </si>
+  <si>
+    <t>also supported</t>
+  </si>
+  <si>
+    <t>are also supported</t>
+  </si>
+  <si>
+    <t>and can</t>
+  </si>
+  <si>
+    <t>and can be</t>
+  </si>
+  <si>
+    <t>for multiple</t>
+  </si>
+  <si>
+    <t>multiple novels</t>
+  </si>
+  <si>
+    <t>for multiple novels</t>
+  </si>
+  <si>
+    <t>novels this</t>
+  </si>
+  <si>
+    <t>multiple novels this</t>
+  </si>
+  <si>
+    <t>spaces and</t>
+  </si>
+  <si>
+    <t>of quotes</t>
+  </si>
+  <si>
+    <t>also add</t>
+  </si>
+  <si>
+    <t>can also add</t>
+  </si>
+  <si>
+    <t>scene is</t>
+  </si>
+  <si>
+    <t>by a</t>
+  </si>
+  <si>
+    <t>from the</t>
+  </si>
+  <si>
+    <t>the syntax</t>
+  </si>
+  <si>
+    <t>syntax highlighter</t>
+  </si>
+  <si>
+    <t>the syntax highlighter</t>
+  </si>
+  <si>
+    <t>be automatically</t>
+  </si>
+  <si>
+    <t>can be automatically</t>
+  </si>
+  <si>
+    <t>the editor</t>
+  </si>
+  <si>
+    <t>this paragraph</t>
+  </si>
+  <si>
+    <t>the project</t>
+  </si>
+  <si>
+    <t>have the</t>
+  </si>
+  <si>
+    <t>formatting of</t>
+  </si>
+  <si>
+    <t>when you</t>
+  </si>
+  <si>
+    <t>as a</t>
+  </si>
+  <si>
+    <t>heading like</t>
+  </si>
+  <si>
+    <t>heading like the</t>
+  </si>
+  <si>
+    <t>the one</t>
+  </si>
+  <si>
+    <t>like the one</t>
   </si>
 </sst>
 </file>
@@ -754,32 +1594,32 @@
   <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.84" customWidth="true" style="0"/>
-    <col min="2" max="2" width="22.45" customWidth="true" style="0"/>
-    <col min="3" max="3" width="7.26" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.45" customWidth="true" style="0"/>
-    <col min="5" max="5" width="19.3" customWidth="true" style="0"/>
-    <col min="6" max="6" width="40" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.24" customWidth="true" style="0"/>
+    <col min="2" max="2" width="19.9" customWidth="true" style="0"/>
+    <col min="3" max="3" width="6.96" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.8" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.3" customWidth="true" style="0"/>
+    <col min="6" max="6" width="38.9" customWidth="true" style="0"/>
     <col min="7" max="7" width="40" customWidth="true" style="0"/>
     <col min="8" max="8" width="40" customWidth="true" style="0"/>
     <col min="9" max="9" width="40" customWidth="true" style="0"/>
     <col min="10" max="10" width="40" customWidth="true" style="0"/>
     <col min="11" max="11" width="40" customWidth="true" style="0"/>
     <col min="12" max="12" width="40" customWidth="true" style="0"/>
-    <col min="13" max="13" width="14.94" customWidth="true" style="0"/>
-    <col min="14" max="14" width="14.58" customWidth="true" style="0"/>
-    <col min="15" max="15" width="9.36" customWidth="true" style="0"/>
-    <col min="16" max="16" width="11.7" customWidth="true" style="0"/>
-    <col min="17" max="17" width="18.9" customWidth="true" style="0"/>
-    <col min="18" max="18" width="12.6" customWidth="true" style="0"/>
-    <col min="19" max="19" width="9.6" customWidth="true" style="0"/>
-    <col min="20" max="20" width="17.05" customWidth="true" style="0"/>
+    <col min="13" max="13" width="13.56" customWidth="true" style="0"/>
+    <col min="14" max="14" width="13.68" customWidth="true" style="0"/>
+    <col min="15" max="15" width="8.64" customWidth="true" style="0"/>
+    <col min="16" max="16" width="10.56" customWidth="true" style="0"/>
+    <col min="17" max="17" width="17.76" customWidth="true" style="0"/>
+    <col min="18" max="18" width="11.88" customWidth="true" style="0"/>
+    <col min="19" max="19" width="8.88" customWidth="true" style="0"/>
+    <col min="20" max="20" width="14.7" customWidth="true" style="0"/>
     <col min="21" max="21" width="40" customWidth="true" style="0"/>
-    <col min="22" max="22" width="26.7" customWidth="true" style="0"/>
-    <col min="23" max="23" width="19.15" customWidth="true" style="0"/>
+    <col min="22" max="22" width="24.96" customWidth="true" style="0"/>
+    <col min="23" max="23" width="16.7" customWidth="true" style="0"/>
     <col min="24" max="24" width="40" customWidth="true" style="0"/>
-    <col min="25" max="25" width="3.06" customWidth="true" style="0"/>
-    <col min="26" max="26" width="15.12" customWidth="true" style="0"/>
+    <col min="25" max="25" width="2.64" customWidth="true" style="0"/>
+    <col min="26" max="26" width="14.16" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -909,11 +1749,11 @@
       <c r="P2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="7"/>
+      <c r="Q2" s="4"/>
       <c r="R2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
@@ -970,7 +1810,7 @@
       <c r="Q3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="7"/>
+      <c r="R3" s="4"/>
       <c r="S3" s="7"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -1043,10 +1883,10 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="7"/>
+      <c r="M5" s="4"/>
       <c r="N5" s="5"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
+      <c r="P5" s="4"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -1202,7 +2042,7 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.45" customWidth="true" style="0"/>
+    <col min="1" max="1" width="8.8" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1343,15 +2183,15 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.65" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16.35" customWidth="true" style="0"/>
-    <col min="4" max="4" width="6.3" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10.26" customWidth="true" style="0"/>
-    <col min="6" max="6" width="10.8" customWidth="true" style="0"/>
-    <col min="7" max="7" width="4.5" customWidth="true" style="0"/>
-    <col min="8" max="8" width="14.2" customWidth="true" style="0"/>
-    <col min="9" max="9" width="12.4" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.7" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.2" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14.3" customWidth="true" style="0"/>
+    <col min="4" max="4" width="5.88" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.84" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.32" customWidth="true" style="0"/>
+    <col min="7" max="7" width="4.32" customWidth="true" style="0"/>
+    <col min="8" max="8" width="12.5" customWidth="true" style="0"/>
+    <col min="9" max="9" width="10.5" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1454,9 +2294,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.85" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14.95" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.7" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.24" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.4" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.56" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1488,7 +2328,7 @@
       <c r="B3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
@@ -1513,295 +2353,4219 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.75" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.06" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.35" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.06" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.5" customWidth="true" style="0"/>
+    <col min="2" max="2" width="11.52" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.76" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.64" customWidth="true" style="0"/>
+    <col min="5" max="5" width="19.4" customWidth="true" style="0"/>
+    <col min="6" max="6" width="7.92" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.52" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11.76" customWidth="true" style="0"/>
+    <col min="9" max="9" width="11.64" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="D1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>90</v>
       </c>
-      <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="3">
+        <v>1394.3</v>
+      </c>
+      <c r="D2" s="3">
+        <v>15.49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="H2" s="3">
+        <v>217.0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="3">
+        <v>516.9</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12.92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="H3" s="3">
+        <v>217.5</v>
+      </c>
+      <c r="I3" s="3">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="3">
+        <v>680.3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>17.44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="H4" s="3">
+        <v>223.8</v>
+      </c>
+      <c r="I4" s="3">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" s="3">
+        <v>399.8</v>
+      </c>
+      <c r="D5" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="H5" s="3">
+        <v>223.8</v>
+      </c>
+      <c r="I5" s="3">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="C6" s="3">
+        <v>376.7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>11.77</v>
+      </c>
+      <c r="F6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="H6" s="3">
+        <v>223.8</v>
+      </c>
+      <c r="I6" s="3">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="3">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" s="3">
+        <v>288.7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>10.69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="H7" s="3">
+        <v>227.8</v>
+      </c>
+      <c r="I7" s="3">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" s="3">
+        <v>256.8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10.27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" s="3">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3">
+        <v>94.9</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="C9" s="3">
+        <v>402.2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>17.49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" s="3">
+        <v>192.5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="F10" t="s">
+        <v>198</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3">
+        <v>129.4</v>
+      </c>
+      <c r="I10" s="3">
+        <v>16.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="C11" s="3">
+        <v>346.3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>17.32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G11" s="3">
+        <v>8</v>
+      </c>
+      <c r="H11" s="3">
+        <v>94.9</v>
+      </c>
+      <c r="I11" s="3">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="C12" s="3">
+        <v>394.3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>23.19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I12" s="3">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="C13" s="3">
+        <v>335.0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>19.71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="3">
+        <v>8</v>
+      </c>
+      <c r="H13" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B14" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" s="3">
+        <v>214.7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>13.42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>202</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="C15" s="3">
+        <v>134.6</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" s="3">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I15" s="3">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="C16" s="3">
+        <v>106.4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>6.65</v>
+      </c>
+      <c r="F16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G16" s="3">
+        <v>7</v>
+      </c>
+      <c r="H16" s="3">
+        <v>94.9</v>
+      </c>
+      <c r="I16" s="3">
+        <v>13.56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="C17" s="3">
+        <v>195.0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="3">
+        <v>7</v>
+      </c>
+      <c r="H17" s="3">
+        <v>94.9</v>
+      </c>
+      <c r="I17" s="3">
+        <v>13.56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="C18" s="3">
+        <v>177.6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>11.84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="3">
+        <v>7</v>
+      </c>
+      <c r="H18" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="C19" s="3">
+        <v>344.9</v>
+      </c>
+      <c r="D19" s="3">
+        <v>24.64</v>
+      </c>
+      <c r="F19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" s="3">
+        <v>7</v>
+      </c>
+      <c r="H19" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I19" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B20" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="C20" s="3">
+        <v>223.8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>15.99</v>
+      </c>
+      <c r="F20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G20" s="3">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B21" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="C21" s="3">
+        <v>219.5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>15.68</v>
+      </c>
+      <c r="F21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G21" s="3">
+        <v>7</v>
+      </c>
+      <c r="H21" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B22" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="C22" s="3">
+        <v>217.5</v>
+      </c>
+      <c r="D22" s="3">
+        <v>15.54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>210</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B23" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="C23" s="3">
+        <v>196.5</v>
+      </c>
+      <c r="D23" s="3">
+        <v>14.04</v>
+      </c>
+      <c r="F23" t="s">
+        <v>211</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B24" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="C24" s="3">
+        <v>238.4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>18.34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>212</v>
+      </c>
+      <c r="G24" s="3">
+        <v>7</v>
+      </c>
+      <c r="H24" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="C25" s="3">
+        <v>223.8</v>
+      </c>
+      <c r="D25" s="3">
+        <v>17.22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>213</v>
+      </c>
+      <c r="G25" s="3">
+        <v>7</v>
+      </c>
+      <c r="H25" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I25" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="C26" s="3">
+        <v>227.8</v>
+      </c>
+      <c r="D26" s="3">
+        <v>18.98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>214</v>
+      </c>
+      <c r="G26" s="3">
+        <v>7</v>
+      </c>
+      <c r="H26" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B27" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="C27" s="3">
+        <v>227.8</v>
+      </c>
+      <c r="D27" s="3">
+        <v>18.98</v>
+      </c>
+      <c r="F27" t="s">
+        <v>215</v>
+      </c>
+      <c r="G27" s="3">
+        <v>7</v>
+      </c>
+      <c r="H27" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B28" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="C28" s="3">
+        <v>195.0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G28" s="3">
+        <v>7</v>
+      </c>
+      <c r="H28" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I28" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B29" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="C29" s="3">
+        <v>119.5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>9.96</v>
+      </c>
+      <c r="F29" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" s="3">
+        <v>7</v>
+      </c>
+      <c r="H29" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="3">
         <v>10</v>
+      </c>
+      <c r="C30" s="3">
+        <v>156.3</v>
+      </c>
+      <c r="D30" s="3">
+        <v>15.63</v>
+      </c>
+      <c r="F30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="3">
+        <v>6</v>
+      </c>
+      <c r="H30" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I30" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="3">
+        <v>9</v>
+      </c>
+      <c r="C31" s="3">
+        <v>170.2</v>
+      </c>
+      <c r="D31" s="3">
+        <v>18.91</v>
+      </c>
+      <c r="F31" t="s">
+        <v>219</v>
+      </c>
+      <c r="G31" s="3">
+        <v>6</v>
+      </c>
+      <c r="H31" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I31" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="3">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3">
+        <v>94.9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>10.54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>220</v>
+      </c>
+      <c r="G32" s="3">
+        <v>6</v>
+      </c>
+      <c r="H32" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="3">
+        <v>8</v>
+      </c>
+      <c r="C33" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D33" s="3">
+        <v>9.31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>221</v>
+      </c>
+      <c r="G33" s="3">
+        <v>6</v>
+      </c>
+      <c r="H33" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="3">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3">
+        <v>135.5</v>
+      </c>
+      <c r="D34" s="3">
+        <v>19.36</v>
+      </c>
+      <c r="F34" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="3">
+        <v>6</v>
+      </c>
+      <c r="H34" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I34" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="3">
+        <v>7</v>
+      </c>
+      <c r="C35" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D35" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F35" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="3">
+        <v>6</v>
+      </c>
+      <c r="H35" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I35" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="3">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D36" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F36" t="s">
+        <v>224</v>
+      </c>
+      <c r="G36" s="3">
+        <v>6</v>
+      </c>
+      <c r="H36" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I36" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="3">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D37" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F37" t="s">
+        <v>225</v>
+      </c>
+      <c r="G37" s="3">
+        <v>6</v>
+      </c>
+      <c r="H37" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I37" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3">
+        <v>7</v>
+      </c>
+      <c r="C38" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D38" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F38" t="s">
+        <v>226</v>
+      </c>
+      <c r="G38" s="3">
+        <v>6</v>
+      </c>
+      <c r="H38" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I38" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="3">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D39" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G39" s="3">
+        <v>6</v>
+      </c>
+      <c r="H39" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I39" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="3">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D40" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F40" t="s">
+        <v>228</v>
+      </c>
+      <c r="G40" s="3">
+        <v>6</v>
+      </c>
+      <c r="H40" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I40" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="3">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D41" s="3">
+        <v>10.64</v>
+      </c>
+      <c r="F41" t="s">
+        <v>229</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6</v>
+      </c>
+      <c r="H41" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I41" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="3">
+        <v>6</v>
+      </c>
+      <c r="C42" s="3">
+        <v>76.7</v>
+      </c>
+      <c r="D42" s="3">
+        <v>12.78</v>
+      </c>
+      <c r="F42" t="s">
+        <v>230</v>
+      </c>
+      <c r="G42" s="3">
+        <v>6</v>
+      </c>
+      <c r="H42" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I42" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="3">
+        <v>6</v>
+      </c>
+      <c r="C43" s="3">
+        <v>75.5</v>
+      </c>
+      <c r="D43" s="3">
+        <v>12.58</v>
+      </c>
+      <c r="F43" t="s">
+        <v>231</v>
+      </c>
+      <c r="G43" s="3">
+        <v>6</v>
+      </c>
+      <c r="H43" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I43" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="3">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D44" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F44" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="3">
+        <v>6</v>
+      </c>
+      <c r="H44" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I44" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="3">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D45" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F45" t="s">
+        <v>233</v>
+      </c>
+      <c r="G45" s="3">
+        <v>6</v>
+      </c>
+      <c r="H45" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I45" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="3">
+        <v>6</v>
+      </c>
+      <c r="C46" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" s="3">
+        <v>6</v>
+      </c>
+      <c r="H46" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I46" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="3">
+        <v>6</v>
+      </c>
+      <c r="C47" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D47" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F47" t="s">
+        <v>235</v>
+      </c>
+      <c r="G47" s="3">
+        <v>6</v>
+      </c>
+      <c r="H47" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I47" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="3">
+        <v>6</v>
+      </c>
+      <c r="C48" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D48" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F48" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6</v>
+      </c>
+      <c r="H48" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I48" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="3">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D49" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>237</v>
+      </c>
+      <c r="G49" s="3">
+        <v>6</v>
+      </c>
+      <c r="H49" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I49" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="3">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D50" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F50" t="s">
+        <v>238</v>
+      </c>
+      <c r="G50" s="3">
+        <v>6</v>
+      </c>
+      <c r="H50" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I50" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="3">
+        <v>6</v>
+      </c>
+      <c r="C51" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D51" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>239</v>
+      </c>
+      <c r="G51" s="3">
+        <v>6</v>
+      </c>
+      <c r="H51" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="3">
+        <v>6</v>
+      </c>
+      <c r="C52" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D52" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F52" t="s">
+        <v>240</v>
+      </c>
+      <c r="G52" s="3">
+        <v>6</v>
+      </c>
+      <c r="H52" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" s="3">
+        <v>6</v>
+      </c>
+      <c r="C53" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D53" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F53" t="s">
+        <v>241</v>
+      </c>
+      <c r="G53" s="3">
+        <v>6</v>
+      </c>
+      <c r="H53" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I53" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="3">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D54" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F54" t="s">
+        <v>242</v>
+      </c>
+      <c r="G54" s="3">
+        <v>6</v>
+      </c>
+      <c r="H54" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I54" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="3">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D55" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F55" t="s">
+        <v>243</v>
+      </c>
+      <c r="G55" s="3">
+        <v>6</v>
+      </c>
+      <c r="H55" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I55" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="3">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="D56" s="3">
+        <v>12.42</v>
+      </c>
+      <c r="F56" t="s">
+        <v>244</v>
+      </c>
+      <c r="G56" s="3">
+        <v>6</v>
+      </c>
+      <c r="H56" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I56" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" s="3">
+        <v>5</v>
+      </c>
+      <c r="C57" s="3">
+        <v>84.7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>16.94</v>
+      </c>
+      <c r="F57" t="s">
+        <v>245</v>
+      </c>
+      <c r="G57" s="3">
+        <v>6</v>
+      </c>
+      <c r="H57" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I57" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="3">
+        <v>5</v>
+      </c>
+      <c r="C58" s="3">
+        <v>78.1</v>
+      </c>
+      <c r="D58" s="3">
+        <v>15.62</v>
+      </c>
+      <c r="F58" t="s">
+        <v>246</v>
+      </c>
+      <c r="G58" s="3">
+        <v>6</v>
+      </c>
+      <c r="H58" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I58" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="3">
+        <v>5</v>
+      </c>
+      <c r="C59" s="3">
+        <v>74.9</v>
+      </c>
+      <c r="D59" s="3">
+        <v>14.98</v>
+      </c>
+      <c r="F59" t="s">
+        <v>247</v>
+      </c>
+      <c r="G59" s="3">
+        <v>6</v>
+      </c>
+      <c r="H59" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I59" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="3">
+        <v>5</v>
+      </c>
+      <c r="C60" s="3">
+        <v>62.9</v>
+      </c>
+      <c r="D60" s="3">
+        <v>12.58</v>
+      </c>
+      <c r="F60" t="s">
+        <v>248</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6</v>
+      </c>
+      <c r="H60" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I60" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" s="3">
+        <v>4</v>
+      </c>
+      <c r="C61" s="3">
+        <v>86.8</v>
+      </c>
+      <c r="D61" s="3">
+        <v>21.7</v>
+      </c>
+      <c r="F61" t="s">
+        <v>249</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6</v>
+      </c>
+      <c r="H61" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I61" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="3">
+        <v>4</v>
+      </c>
+      <c r="C62" s="3">
+        <v>69.1</v>
+      </c>
+      <c r="D62" s="3">
+        <v>17.28</v>
+      </c>
+      <c r="F62" t="s">
+        <v>250</v>
+      </c>
+      <c r="G62" s="3">
+        <v>6</v>
+      </c>
+      <c r="H62" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I62" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="3">
+        <v>4</v>
+      </c>
+      <c r="C63" s="3">
+        <v>56.4</v>
+      </c>
+      <c r="D63" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>251</v>
+      </c>
+      <c r="G63" s="3">
+        <v>6</v>
+      </c>
+      <c r="H63" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I63" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" s="3">
+        <v>4</v>
+      </c>
+      <c r="C64" s="3">
+        <v>54.3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>13.58</v>
+      </c>
+      <c r="F64" t="s">
+        <v>252</v>
+      </c>
+      <c r="G64" s="3">
+        <v>6</v>
+      </c>
+      <c r="H64" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I64" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="3">
+        <v>4</v>
+      </c>
+      <c r="C65" s="3">
+        <v>32.6</v>
+      </c>
+      <c r="D65" s="3">
+        <v>8.15</v>
+      </c>
+      <c r="F65" t="s">
+        <v>253</v>
+      </c>
+      <c r="G65" s="3">
+        <v>6</v>
+      </c>
+      <c r="H65" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I65" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>150</v>
+      </c>
+      <c r="B66" s="3">
+        <v>4</v>
+      </c>
+      <c r="C66" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="D66" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="F66" t="s">
+        <v>254</v>
+      </c>
+      <c r="G66" s="3">
+        <v>6</v>
+      </c>
+      <c r="H66" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I66" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="3">
+        <v>3</v>
+      </c>
+      <c r="C67" s="3">
+        <v>159.1</v>
+      </c>
+      <c r="D67" s="3">
+        <v>53.03</v>
+      </c>
+      <c r="F67" t="s">
+        <v>255</v>
+      </c>
+      <c r="G67" s="3">
+        <v>6</v>
+      </c>
+      <c r="H67" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I67" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="3">
+        <v>3</v>
+      </c>
+      <c r="C68" s="3">
+        <v>70.6</v>
+      </c>
+      <c r="D68" s="3">
+        <v>23.53</v>
+      </c>
+      <c r="F68" t="s">
+        <v>256</v>
+      </c>
+      <c r="G68" s="3">
+        <v>6</v>
+      </c>
+      <c r="H68" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I68" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="3">
+        <v>3</v>
+      </c>
+      <c r="C69" s="3">
+        <v>67.8</v>
+      </c>
+      <c r="D69" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="F69" t="s">
+        <v>257</v>
+      </c>
+      <c r="G69" s="3">
+        <v>6</v>
+      </c>
+      <c r="H69" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I69" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="3">
+        <v>3</v>
+      </c>
+      <c r="C70" s="3">
+        <v>65.2</v>
+      </c>
+      <c r="D70" s="3">
+        <v>21.73</v>
+      </c>
+      <c r="F70" t="s">
+        <v>258</v>
+      </c>
+      <c r="G70" s="3">
+        <v>6</v>
+      </c>
+      <c r="H70" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I70" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" s="3">
+        <v>3</v>
+      </c>
+      <c r="C71" s="3">
+        <v>64.9</v>
+      </c>
+      <c r="D71" s="3">
+        <v>21.63</v>
+      </c>
+      <c r="F71" t="s">
+        <v>259</v>
+      </c>
+      <c r="G71" s="3">
+        <v>6</v>
+      </c>
+      <c r="H71" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I71" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="3">
+        <v>3</v>
+      </c>
+      <c r="C72" s="3">
+        <v>64.8</v>
+      </c>
+      <c r="D72" s="3">
+        <v>21.6</v>
+      </c>
+      <c r="F72" t="s">
+        <v>260</v>
+      </c>
+      <c r="G72" s="3">
+        <v>6</v>
+      </c>
+      <c r="H72" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I72" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>157</v>
+      </c>
+      <c r="B73" s="3">
+        <v>3</v>
+      </c>
+      <c r="C73" s="3">
+        <v>62.0</v>
+      </c>
+      <c r="D73" s="3">
+        <v>20.67</v>
+      </c>
+      <c r="F73" t="s">
+        <v>261</v>
+      </c>
+      <c r="G73" s="3">
+        <v>6</v>
+      </c>
+      <c r="H73" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I73" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="3">
+        <v>3</v>
+      </c>
+      <c r="C74" s="3">
+        <v>48.4</v>
+      </c>
+      <c r="D74" s="3">
+        <v>16.13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>262</v>
+      </c>
+      <c r="G74" s="3">
+        <v>6</v>
+      </c>
+      <c r="H74" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I74" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="3">
+        <v>3</v>
+      </c>
+      <c r="C75" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="D75" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>263</v>
+      </c>
+      <c r="G75" s="3">
+        <v>6</v>
+      </c>
+      <c r="H75" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I75" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>160</v>
+      </c>
+      <c r="B76" s="3">
+        <v>3</v>
+      </c>
+      <c r="C76" s="3">
+        <v>35.1</v>
+      </c>
+      <c r="D76" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="F76" t="s">
+        <v>264</v>
+      </c>
+      <c r="G76" s="3">
+        <v>6</v>
+      </c>
+      <c r="H76" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I76" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" s="3">
+        <v>3</v>
+      </c>
+      <c r="C77" s="3">
+        <v>34.1</v>
+      </c>
+      <c r="D77" s="3">
+        <v>11.37</v>
+      </c>
+      <c r="F77" t="s">
+        <v>265</v>
+      </c>
+      <c r="G77" s="3">
+        <v>6</v>
+      </c>
+      <c r="H77" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I77" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="3">
+        <v>3</v>
+      </c>
+      <c r="C78" s="3">
+        <v>33.9</v>
+      </c>
+      <c r="D78" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>266</v>
+      </c>
+      <c r="G78" s="3">
+        <v>6</v>
+      </c>
+      <c r="H78" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I78" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="3">
+        <v>3</v>
+      </c>
+      <c r="C79" s="3">
+        <v>32.7</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="F79" t="s">
+        <v>267</v>
+      </c>
+      <c r="G79" s="3">
+        <v>6</v>
+      </c>
+      <c r="H79" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I79" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="3">
+        <v>3</v>
+      </c>
+      <c r="C80" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="D80" s="3">
+        <v>8.83</v>
+      </c>
+      <c r="F80" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" s="3">
+        <v>6</v>
+      </c>
+      <c r="H80" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I80" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" s="3">
+        <v>3</v>
+      </c>
+      <c r="C81" s="3">
+        <v>26.1</v>
+      </c>
+      <c r="D81" s="3">
+        <v>8.7</v>
+      </c>
+      <c r="F81" t="s">
+        <v>269</v>
+      </c>
+      <c r="G81" s="3">
+        <v>6</v>
+      </c>
+      <c r="H81" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>166</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3">
+        <v>59.1</v>
+      </c>
+      <c r="D82" s="3">
+        <v>29.55</v>
+      </c>
+      <c r="F82" t="s">
+        <v>270</v>
+      </c>
+      <c r="G82" s="3">
+        <v>6</v>
+      </c>
+      <c r="H82" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I82" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="3">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3">
+        <v>59.1</v>
+      </c>
+      <c r="D83" s="3">
+        <v>29.55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>271</v>
+      </c>
+      <c r="G83" s="3">
+        <v>6</v>
+      </c>
+      <c r="H83" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I83" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3">
+        <v>59.1</v>
+      </c>
+      <c r="D84" s="3">
+        <v>29.55</v>
+      </c>
+      <c r="F84" t="s">
+        <v>272</v>
+      </c>
+      <c r="G84" s="3">
+        <v>6</v>
+      </c>
+      <c r="H84" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I84" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="3">
+        <v>2</v>
+      </c>
+      <c r="C85" s="3">
+        <v>59.1</v>
+      </c>
+      <c r="D85" s="3">
+        <v>29.55</v>
+      </c>
+      <c r="F85" t="s">
+        <v>273</v>
+      </c>
+      <c r="G85" s="3">
+        <v>6</v>
+      </c>
+      <c r="H85" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I85" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="D86" s="3">
+        <v>23.85</v>
+      </c>
+      <c r="F86" t="s">
+        <v>274</v>
+      </c>
+      <c r="G86" s="3">
+        <v>6</v>
+      </c>
+      <c r="H86" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I86" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="3">
+        <v>2</v>
+      </c>
+      <c r="C87" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="D87" s="3">
+        <v>23.85</v>
+      </c>
+      <c r="F87" t="s">
+        <v>275</v>
+      </c>
+      <c r="G87" s="3">
+        <v>6</v>
+      </c>
+      <c r="H87" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I87" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3">
+        <v>38.3</v>
+      </c>
+      <c r="D88" s="3">
+        <v>19.15</v>
+      </c>
+      <c r="F88" t="s">
+        <v>276</v>
+      </c>
+      <c r="G88" s="3">
+        <v>6</v>
+      </c>
+      <c r="H88" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I88" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" s="3">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3">
+        <v>38.3</v>
+      </c>
+      <c r="D89" s="3">
+        <v>19.15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>277</v>
+      </c>
+      <c r="G89" s="3">
+        <v>6</v>
+      </c>
+      <c r="H89" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I89" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>174</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3">
+        <v>33.9</v>
+      </c>
+      <c r="D90" s="3">
+        <v>16.95</v>
+      </c>
+      <c r="F90" t="s">
+        <v>278</v>
+      </c>
+      <c r="G90" s="3">
+        <v>6</v>
+      </c>
+      <c r="H90" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I90" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>175</v>
+      </c>
+      <c r="B91" s="3">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3">
+        <v>33.9</v>
+      </c>
+      <c r="D91" s="3">
+        <v>16.95</v>
+      </c>
+      <c r="F91" t="s">
+        <v>279</v>
+      </c>
+      <c r="G91" s="3">
+        <v>6</v>
+      </c>
+      <c r="H91" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I91" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" s="3">
+        <v>2</v>
+      </c>
+      <c r="C92" s="3">
+        <v>32.5</v>
+      </c>
+      <c r="D92" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="F92" t="s">
+        <v>280</v>
+      </c>
+      <c r="G92" s="3">
+        <v>6</v>
+      </c>
+      <c r="H92" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I92" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="3">
+        <v>2</v>
+      </c>
+      <c r="C93" s="3">
+        <v>32.5</v>
+      </c>
+      <c r="D93" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="F93" t="s">
+        <v>281</v>
+      </c>
+      <c r="G93" s="3">
+        <v>6</v>
+      </c>
+      <c r="H93" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I93" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>178</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3">
+        <v>32.5</v>
+      </c>
+      <c r="D94" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="F94" t="s">
+        <v>282</v>
+      </c>
+      <c r="G94" s="3">
+        <v>6</v>
+      </c>
+      <c r="H94" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I94" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>179</v>
+      </c>
+      <c r="B95" s="3">
+        <v>2</v>
+      </c>
+      <c r="C95" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="D95" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="F95" t="s">
+        <v>283</v>
+      </c>
+      <c r="G95" s="3">
+        <v>6</v>
+      </c>
+      <c r="H95" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I95" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>180</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="D96" s="3">
+        <v>14.05</v>
+      </c>
+      <c r="F96" t="s">
+        <v>284</v>
+      </c>
+      <c r="G96" s="3">
+        <v>6</v>
+      </c>
+      <c r="H96" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I96" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>181</v>
+      </c>
+      <c r="B97" s="3">
+        <v>2</v>
+      </c>
+      <c r="C97" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="D97" s="3">
+        <v>14.05</v>
+      </c>
+      <c r="F97" t="s">
+        <v>285</v>
+      </c>
+      <c r="G97" s="3">
+        <v>6</v>
+      </c>
+      <c r="H97" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I97" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="D98" s="3">
+        <v>13.25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>286</v>
+      </c>
+      <c r="G98" s="3">
+        <v>6</v>
+      </c>
+      <c r="H98" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I98" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" s="3">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="D99" s="3">
+        <v>13.25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>287</v>
+      </c>
+      <c r="G99" s="3">
+        <v>6</v>
+      </c>
+      <c r="H99" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I99" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2</v>
+      </c>
+      <c r="C100" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="D100" s="3">
+        <v>12.85</v>
+      </c>
+      <c r="F100" t="s">
+        <v>288</v>
+      </c>
+      <c r="G100" s="3">
+        <v>6</v>
+      </c>
+      <c r="H100" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I100" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" s="3">
+        <v>2</v>
+      </c>
+      <c r="C101" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="D101" s="3">
+        <v>11.85</v>
+      </c>
+      <c r="F101" t="s">
+        <v>289</v>
+      </c>
+      <c r="G101" s="3">
+        <v>6</v>
+      </c>
+      <c r="H101" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I101" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102" s="3">
+        <v>2</v>
+      </c>
+      <c r="C102" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="D102" s="3">
+        <v>11.65</v>
+      </c>
+      <c r="F102" t="s">
+        <v>290</v>
+      </c>
+      <c r="G102" s="3">
+        <v>6</v>
+      </c>
+      <c r="H102" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I102" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" s="3">
+        <v>2</v>
+      </c>
+      <c r="C103" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="D103" s="3">
+        <v>11.45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>291</v>
+      </c>
+      <c r="G103" s="3">
+        <v>6</v>
+      </c>
+      <c r="H103" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I103" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>188</v>
+      </c>
+      <c r="B104" s="3">
+        <v>2</v>
+      </c>
+      <c r="C104" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="D104" s="3">
+        <v>11.45</v>
+      </c>
+      <c r="F104" t="s">
+        <v>292</v>
+      </c>
+      <c r="G104" s="3">
+        <v>6</v>
+      </c>
+      <c r="H104" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I104" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>189</v>
+      </c>
+      <c r="B105" s="3">
+        <v>2</v>
+      </c>
+      <c r="C105" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="D105" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="F105" t="s">
+        <v>293</v>
+      </c>
+      <c r="G105" s="3">
+        <v>6</v>
+      </c>
+      <c r="H105" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I105" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="F106" t="s">
+        <v>294</v>
+      </c>
+      <c r="G106" s="3">
+        <v>6</v>
+      </c>
+      <c r="H106" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I106" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="F107" t="s">
+        <v>295</v>
+      </c>
+      <c r="G107" s="3">
+        <v>6</v>
+      </c>
+      <c r="H107" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I107" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="F108" t="s">
+        <v>296</v>
+      </c>
+      <c r="G108" s="3">
+        <v>6</v>
+      </c>
+      <c r="H108" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I108" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="F109" t="s">
+        <v>297</v>
+      </c>
+      <c r="G109" s="3">
+        <v>6</v>
+      </c>
+      <c r="H109" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I109" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="F110" t="s">
+        <v>298</v>
+      </c>
+      <c r="G110" s="3">
+        <v>6</v>
+      </c>
+      <c r="H110" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I110" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="F111" t="s">
+        <v>299</v>
+      </c>
+      <c r="G111" s="3">
+        <v>6</v>
+      </c>
+      <c r="H111" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I111" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="F112" t="s">
+        <v>300</v>
+      </c>
+      <c r="G112" s="3">
+        <v>6</v>
+      </c>
+      <c r="H112" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I112" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="F113" t="s">
+        <v>301</v>
+      </c>
+      <c r="G113" s="3">
+        <v>6</v>
+      </c>
+      <c r="H113" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I113" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="F114" t="s">
+        <v>302</v>
+      </c>
+      <c r="G114" s="3">
+        <v>6</v>
+      </c>
+      <c r="H114" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I114" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="F115" t="s">
+        <v>303</v>
+      </c>
+      <c r="G115" s="3">
+        <v>6</v>
+      </c>
+      <c r="H115" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I115" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="F116" t="s">
+        <v>304</v>
+      </c>
+      <c r="G116" s="3">
+        <v>6</v>
+      </c>
+      <c r="H116" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I116" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="F117" t="s">
+        <v>305</v>
+      </c>
+      <c r="G117" s="3">
+        <v>6</v>
+      </c>
+      <c r="H117" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I117" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="F118" t="s">
+        <v>306</v>
+      </c>
+      <c r="G118" s="3">
+        <v>6</v>
+      </c>
+      <c r="H118" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I118" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="F119" t="s">
+        <v>307</v>
+      </c>
+      <c r="G119" s="3">
+        <v>6</v>
+      </c>
+      <c r="H119" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I119" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="F120" t="s">
+        <v>308</v>
+      </c>
+      <c r="G120" s="3">
+        <v>6</v>
+      </c>
+      <c r="H120" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I120" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="F121" t="s">
+        <v>309</v>
+      </c>
+      <c r="G121" s="3">
+        <v>6</v>
+      </c>
+      <c r="H121" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I121" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="F122" t="s">
+        <v>310</v>
+      </c>
+      <c r="G122" s="3">
+        <v>6</v>
+      </c>
+      <c r="H122" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I122" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="F123" t="s">
+        <v>311</v>
+      </c>
+      <c r="G123" s="3">
+        <v>6</v>
+      </c>
+      <c r="H123" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I123" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="F124" t="s">
+        <v>312</v>
+      </c>
+      <c r="G124" s="3">
+        <v>6</v>
+      </c>
+      <c r="H124" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I124" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="F125" t="s">
+        <v>313</v>
+      </c>
+      <c r="G125" s="3">
+        <v>6</v>
+      </c>
+      <c r="H125" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I125" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="F126" t="s">
+        <v>314</v>
+      </c>
+      <c r="G126" s="3">
+        <v>6</v>
+      </c>
+      <c r="H126" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I126" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="F127" t="s">
+        <v>315</v>
+      </c>
+      <c r="G127" s="3">
+        <v>6</v>
+      </c>
+      <c r="H127" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I127" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="F128" t="s">
+        <v>316</v>
+      </c>
+      <c r="G128" s="3">
+        <v>6</v>
+      </c>
+      <c r="H128" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I128" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="F129" t="s">
+        <v>317</v>
+      </c>
+      <c r="G129" s="3">
+        <v>6</v>
+      </c>
+      <c r="H129" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I129" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="F130" t="s">
+        <v>318</v>
+      </c>
+      <c r="G130" s="3">
+        <v>6</v>
+      </c>
+      <c r="H130" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I130" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="F131" t="s">
+        <v>319</v>
+      </c>
+      <c r="G131" s="3">
+        <v>6</v>
+      </c>
+      <c r="H131" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I131" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="F132" t="s">
+        <v>320</v>
+      </c>
+      <c r="G132" s="3">
+        <v>6</v>
+      </c>
+      <c r="H132" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I132" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="F133" t="s">
+        <v>321</v>
+      </c>
+      <c r="G133" s="3">
+        <v>6</v>
+      </c>
+      <c r="H133" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I133" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="F134" t="s">
+        <v>322</v>
+      </c>
+      <c r="G134" s="3">
+        <v>6</v>
+      </c>
+      <c r="H134" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I134" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="F135" t="s">
+        <v>323</v>
+      </c>
+      <c r="G135" s="3">
+        <v>6</v>
+      </c>
+      <c r="H135" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I135" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="F136" t="s">
+        <v>324</v>
+      </c>
+      <c r="G136" s="3">
+        <v>6</v>
+      </c>
+      <c r="H136" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I136" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="F137" t="s">
+        <v>325</v>
+      </c>
+      <c r="G137" s="3">
+        <v>6</v>
+      </c>
+      <c r="H137" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I137" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="F138" t="s">
+        <v>326</v>
+      </c>
+      <c r="G138" s="3">
+        <v>6</v>
+      </c>
+      <c r="H138" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I138" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="F139" t="s">
+        <v>327</v>
+      </c>
+      <c r="G139" s="3">
+        <v>6</v>
+      </c>
+      <c r="H139" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I139" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="F140" t="s">
+        <v>328</v>
+      </c>
+      <c r="G140" s="3">
+        <v>6</v>
+      </c>
+      <c r="H140" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I140" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="F141" t="s">
+        <v>329</v>
+      </c>
+      <c r="G141" s="3">
+        <v>6</v>
+      </c>
+      <c r="H141" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I141" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="F142" t="s">
+        <v>330</v>
+      </c>
+      <c r="G142" s="3">
+        <v>6</v>
+      </c>
+      <c r="H142" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I142" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="F143" t="s">
+        <v>331</v>
+      </c>
+      <c r="G143" s="3">
+        <v>6</v>
+      </c>
+      <c r="H143" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I143" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="F144" t="s">
+        <v>332</v>
+      </c>
+      <c r="G144" s="3">
+        <v>6</v>
+      </c>
+      <c r="H144" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I144" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="F145" t="s">
+        <v>333</v>
+      </c>
+      <c r="G145" s="3">
+        <v>6</v>
+      </c>
+      <c r="H145" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I145" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="F146" t="s">
+        <v>334</v>
+      </c>
+      <c r="G146" s="3">
+        <v>6</v>
+      </c>
+      <c r="H146" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I146" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="F147" t="s">
+        <v>335</v>
+      </c>
+      <c r="G147" s="3">
+        <v>6</v>
+      </c>
+      <c r="H147" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I147" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="F148" t="s">
+        <v>336</v>
+      </c>
+      <c r="G148" s="3">
+        <v>6</v>
+      </c>
+      <c r="H148" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I148" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="F149" t="s">
+        <v>337</v>
+      </c>
+      <c r="G149" s="3">
+        <v>6</v>
+      </c>
+      <c r="H149" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I149" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="F150" t="s">
+        <v>338</v>
+      </c>
+      <c r="G150" s="3">
+        <v>6</v>
+      </c>
+      <c r="H150" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I150" s="3">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="F151" t="s">
+        <v>339</v>
+      </c>
+      <c r="G151" s="3">
+        <v>5</v>
+      </c>
+      <c r="H151" s="3">
+        <v>76.2</v>
+      </c>
+      <c r="I151" s="3">
+        <v>15.24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="F152" t="s">
+        <v>340</v>
+      </c>
+      <c r="G152" s="3">
+        <v>5</v>
+      </c>
+      <c r="H152" s="3">
+        <v>76.2</v>
+      </c>
+      <c r="I152" s="3">
+        <v>15.24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="F153" t="s">
+        <v>341</v>
+      </c>
+      <c r="G153" s="3">
+        <v>5</v>
+      </c>
+      <c r="H153" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="I153" s="3">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="F154" t="s">
+        <v>342</v>
+      </c>
+      <c r="G154" s="3">
+        <v>4</v>
+      </c>
+      <c r="H154" s="3">
+        <v>99.7</v>
+      </c>
+      <c r="I154" s="3">
+        <v>24.93</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="F155" t="s">
+        <v>343</v>
+      </c>
+      <c r="G155" s="3">
+        <v>4</v>
+      </c>
+      <c r="H155" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="I155" s="3">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="F156" t="s">
+        <v>344</v>
+      </c>
+      <c r="G156" s="3">
+        <v>4</v>
+      </c>
+      <c r="H156" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="I156" s="3">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="F157" t="s">
+        <v>345</v>
+      </c>
+      <c r="G157" s="3">
+        <v>4</v>
+      </c>
+      <c r="H157" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="I157" s="3">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="F158" t="s">
+        <v>346</v>
+      </c>
+      <c r="G158" s="3">
+        <v>3</v>
+      </c>
+      <c r="H158" s="3">
+        <v>83.8</v>
+      </c>
+      <c r="I158" s="3">
+        <v>27.93</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="F159" t="s">
+        <v>347</v>
+      </c>
+      <c r="G159" s="3">
+        <v>3</v>
+      </c>
+      <c r="H159" s="3">
+        <v>83.8</v>
+      </c>
+      <c r="I159" s="3">
+        <v>27.93</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="F160" t="s">
+        <v>348</v>
+      </c>
+      <c r="G160" s="3">
+        <v>3</v>
+      </c>
+      <c r="H160" s="3">
+        <v>49.3</v>
+      </c>
+      <c r="I160" s="3">
+        <v>16.43</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="F161" t="s">
+        <v>349</v>
+      </c>
+      <c r="G161" s="3">
+        <v>3</v>
+      </c>
+      <c r="H161" s="3">
+        <v>47.4</v>
+      </c>
+      <c r="I161" s="3">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="F162" t="s">
+        <v>350</v>
+      </c>
+      <c r="G162" s="3">
+        <v>3</v>
+      </c>
+      <c r="H162" s="3">
+        <v>34.7</v>
+      </c>
+      <c r="I162" s="3">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="F163" t="s">
+        <v>351</v>
+      </c>
+      <c r="G163" s="3">
+        <v>3</v>
+      </c>
+      <c r="H163" s="3">
+        <v>32.5</v>
+      </c>
+      <c r="I163" s="3">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="F164" t="s">
+        <v>352</v>
+      </c>
+      <c r="G164" s="3">
+        <v>3</v>
+      </c>
+      <c r="H164" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="I164" s="3">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="F165" t="s">
+        <v>353</v>
+      </c>
+      <c r="G165" s="3">
+        <v>3</v>
+      </c>
+      <c r="H165" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="I165" s="3">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="F166" t="s">
+        <v>354</v>
+      </c>
+      <c r="G166" s="3">
+        <v>2</v>
+      </c>
+      <c r="H166" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="I166" s="3">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="F167" t="s">
+        <v>355</v>
+      </c>
+      <c r="G167" s="3">
+        <v>2</v>
+      </c>
+      <c r="H167" s="3">
+        <v>33.9</v>
+      </c>
+      <c r="I167" s="3">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="F168" t="s">
+        <v>356</v>
+      </c>
+      <c r="G168" s="3">
+        <v>2</v>
+      </c>
+      <c r="H168" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="I168" s="3">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="F169" t="s">
+        <v>357</v>
+      </c>
+      <c r="G169" s="3">
+        <v>2</v>
+      </c>
+      <c r="H169" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="I169" s="3">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="F170" t="s">
+        <v>358</v>
+      </c>
+      <c r="G170" s="3">
+        <v>2</v>
+      </c>
+      <c r="H170" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="I170" s="3">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="F171" t="s">
+        <v>359</v>
+      </c>
+      <c r="G171" s="3">
+        <v>2</v>
+      </c>
+      <c r="H171" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="I171" s="3">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="F172" t="s">
+        <v>360</v>
+      </c>
+      <c r="G172" s="3">
+        <v>2</v>
+      </c>
+      <c r="H172" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="I172" s="3">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="F173" t="s">
+        <v>361</v>
+      </c>
+      <c r="G173" s="3">
+        <v>2</v>
+      </c>
+      <c r="H173" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="I173" s="3">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="F174" t="s">
+        <v>362</v>
+      </c>
+      <c r="G174" s="3">
+        <v>2</v>
+      </c>
+      <c r="H174" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="I174" s="3">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="F175" t="s">
+        <v>363</v>
+      </c>
+      <c r="G175" s="3">
+        <v>2</v>
+      </c>
+      <c r="H175" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="I175" s="3">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="F176" t="s">
+        <v>364</v>
+      </c>
+      <c r="G176" s="3">
+        <v>2</v>
+      </c>
+      <c r="H176" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="I176" s="3">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="F177" t="s">
+        <v>365</v>
+      </c>
+      <c r="G177" s="3">
+        <v>2</v>
+      </c>
+      <c r="H177" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="I177" s="3">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="F178" t="s">
+        <v>366</v>
+      </c>
+      <c r="G178" s="3">
+        <v>2</v>
+      </c>
+      <c r="H178" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="I178" s="3">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="F179" t="s">
+        <v>367</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2</v>
+      </c>
+      <c r="H179" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="I179" s="3">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="F180" t="s">
+        <v>368</v>
+      </c>
+      <c r="G180" s="3">
+        <v>2</v>
+      </c>
+      <c r="H180" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="I180" s="3">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="F181" t="s">
+        <v>369</v>
+      </c>
+      <c r="G181" s="3">
+        <v>2</v>
+      </c>
+      <c r="H181" s="3">
+        <v>24.4</v>
+      </c>
+      <c r="I181" s="3">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="F182" t="s">
+        <v>370</v>
+      </c>
+      <c r="G182" s="3">
+        <v>2</v>
+      </c>
+      <c r="H182" s="3">
+        <v>24.4</v>
+      </c>
+      <c r="I182" s="3">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="F183" t="s">
+        <v>371</v>
+      </c>
+      <c r="G183" s="3">
+        <v>2</v>
+      </c>
+      <c r="H183" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="I183" s="3">
+        <v>11.85</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="F184" t="s">
+        <v>372</v>
+      </c>
+      <c r="G184" s="3">
+        <v>2</v>
+      </c>
+      <c r="H184" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="I184" s="3">
+        <v>11.85</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="F185" t="s">
+        <v>373</v>
+      </c>
+      <c r="G185" s="3">
+        <v>2</v>
+      </c>
+      <c r="H185" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="I185" s="3">
+        <v>11.85</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="F186" t="s">
+        <v>374</v>
+      </c>
+      <c r="G186" s="3">
+        <v>2</v>
+      </c>
+      <c r="H186" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="I186" s="3">
+        <v>11.85</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="F187" t="s">
+        <v>375</v>
+      </c>
+      <c r="G187" s="3">
+        <v>2</v>
+      </c>
+      <c r="H187" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="I187" s="3">
+        <v>11.85</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="F188" t="s">
+        <v>376</v>
+      </c>
+      <c r="G188" s="3">
+        <v>2</v>
+      </c>
+      <c r="H188" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="I188" s="3">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="F189" t="s">
+        <v>377</v>
+      </c>
+      <c r="G189" s="3">
+        <v>2</v>
+      </c>
+      <c r="H189" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="I189" s="3">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="F190" t="s">
+        <v>378</v>
+      </c>
+      <c r="G190" s="3">
+        <v>2</v>
+      </c>
+      <c r="H190" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="I190" s="3">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="F191" t="s">
+        <v>379</v>
+      </c>
+      <c r="G191" s="3">
+        <v>2</v>
+      </c>
+      <c r="H191" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="I191" s="3">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="F192" t="s">
+        <v>380</v>
+      </c>
+      <c r="G192" s="3">
+        <v>2</v>
+      </c>
+      <c r="H192" s="3">
+        <v>19.2</v>
+      </c>
+      <c r="I192" s="3">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="F193" t="s">
+        <v>381</v>
+      </c>
+      <c r="G193" s="3">
+        <v>2</v>
+      </c>
+      <c r="H193" s="3">
+        <v>19.2</v>
+      </c>
+      <c r="I193" s="3">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="F194" t="s">
+        <v>382</v>
+      </c>
+      <c r="G194" s="3">
+        <v>2</v>
+      </c>
+      <c r="H194" s="3">
+        <v>18.7</v>
+      </c>
+      <c r="I194" s="3">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="F195" t="s">
+        <v>383</v>
+      </c>
+      <c r="G195" s="3">
+        <v>2</v>
+      </c>
+      <c r="H195" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="I195" s="3">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="F196" t="s">
+        <v>384</v>
+      </c>
+      <c r="G196" s="3">
+        <v>2</v>
+      </c>
+      <c r="H196" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="I196" s="3">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="F197" t="s">
+        <v>385</v>
+      </c>
+      <c r="G197" s="3">
+        <v>2</v>
+      </c>
+      <c r="H197" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="I197" s="3">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="F198" t="s">
+        <v>386</v>
+      </c>
+      <c r="G198" s="3">
+        <v>2</v>
+      </c>
+      <c r="H198" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="I198" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="F199" t="s">
+        <v>387</v>
+      </c>
+      <c r="G199" s="3">
+        <v>2</v>
+      </c>
+      <c r="H199" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="I199" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="F200" t="s">
+        <v>388</v>
+      </c>
+      <c r="G200" s="3">
+        <v>2</v>
+      </c>
+      <c r="H200" s="3">
+        <v>17.3</v>
+      </c>
+      <c r="I200" s="3">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="F201" t="s">
+        <v>389</v>
+      </c>
+      <c r="G201" s="3">
+        <v>2</v>
+      </c>
+      <c r="H201" s="3">
+        <v>17.3</v>
+      </c>
+      <c r="I201" s="3">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="F202" t="s">
+        <v>390</v>
+      </c>
+      <c r="G202" s="3">
+        <v>2</v>
+      </c>
+      <c r="H202" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="I202" s="3">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="F203" t="s">
+        <v>391</v>
+      </c>
+      <c r="G203" s="3">
+        <v>2</v>
+      </c>
+      <c r="H203" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="I203" s="3">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="F204" t="s">
+        <v>392</v>
+      </c>
+      <c r="G204" s="3">
+        <v>2</v>
+      </c>
+      <c r="H204" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="I204" s="3">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="F205" t="s">
+        <v>393</v>
+      </c>
+      <c r="G205" s="3">
+        <v>2</v>
+      </c>
+      <c r="H205" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="I205" s="3">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="F206" t="s">
+        <v>394</v>
+      </c>
+      <c r="G206" s="3">
+        <v>2</v>
+      </c>
+      <c r="H206" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="I206" s="3">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="F207" t="s">
+        <v>395</v>
+      </c>
+      <c r="G207" s="3">
+        <v>2</v>
+      </c>
+      <c r="H207" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="I207" s="3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="F208" t="s">
+        <v>396</v>
+      </c>
+      <c r="G208" s="3">
+        <v>2</v>
+      </c>
+      <c r="H208" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="I208" s="3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="F209" t="s">
+        <v>397</v>
+      </c>
+      <c r="G209" s="3">
+        <v>2</v>
+      </c>
+      <c r="H209" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="I209" s="3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="F210" t="s">
+        <v>398</v>
+      </c>
+      <c r="G210" s="3">
+        <v>2</v>
+      </c>
+      <c r="H210" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="I210" s="3">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
